--- a/output/2026-10-06_23_Serbia_Grad_Beograd_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-06_23_Serbia_Grad_Beograd_Componentistica_Ventilazione_industriale.xlsx
@@ -474,7 +474,6 @@
           <t>Industrijska Oprema</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Grad Beograd (Zemun)</t>
@@ -490,7 +489,6 @@
           <t>011/3077-086</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Rivenditore di soluzioni tecnologiche per l'aria industriale. Fonte: planplus.rs</t>
@@ -508,7 +506,6 @@
           <t>Etaž d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Grad Beograd (Zemun/Zvezdara/Voždovac)</t>
@@ -524,7 +521,6 @@
           <t>011/3166-265</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Grossista/dettagliante HVAC e ventilazione dal 1990, distributore autorizzato LG dal 2014. Fonte: planplus.rs, lg.com</t>
@@ -542,7 +538,6 @@
           <t>Jakka Group</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Grad Beograd (Novi Beograd)</t>
@@ -558,10 +553,9 @@
           <t>011/2600-901</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ingrosso (veleprodaja) climatizzazione/ventilazione/riscaldamento. Fonte: planplus.rs</t>
+          <t>Ingrosso (veleprodaja) climatizzazione/ventilazione/riscaldamento. Fonte: planplus.rs [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sales company B2B del gruppo Orange Climate (ex Hidria/Lindab); AHU certificate Eurovent, serrande taglia-fuoco, camere bianche. Fonte: oc-impklima.dev.positiva.si, orangeclimate.com</t>
+          <t>Sales company B2B del gruppo Orange Climate (ex Hidria/Lindab); AHU certificate Eurovent, serrande taglia-fuoco, camere bianche. Fonte: oc-impklima.dev.positiva.si, orangeclimate.com [DUPLICATO — vedi anche: 2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,7 +632,6 @@
           <t>011/3099-603</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Grossista dal 1992, oltre 700 installatori serviti; vendita diretta di griglie di ventilazione, ventilatori, recuperatori di calore (verificato via sito ufficiale). Fonte: www.expont.rs, planplus.rs</t>
@@ -671,7 +664,6 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>info@systemair.rs</t>
@@ -694,7 +686,6 @@
           <t>Ecotip Tedex</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Grad Beograd (Zemun)</t>
@@ -710,10 +701,9 @@
           <t>011/2450-976</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Distributore di filtri aria/acqua, parte del gruppo Ecotip (Skopje). Fonte: planplus.rs, amcham.mk</t>
+          <t>Distributore di filtri aria/acqua, parte del gruppo Ecotip (Skopje). Fonte: planplus.rs, amcham.mk [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/output/2026-10-06_23_Serbia_Grad_Beograd_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-06_23_Serbia_Grad_Beograd_Componentistica_Ventilazione_industriale.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
